--- a/wishes.xlsx
+++ b/wishes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="13_ncr:1_{572483D8-A287-5545-9F3E-BD84B65E9158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A48801F4-2D02-2648-B139-160BD258CC66}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="13_ncr:1_{572483D8-A287-5545-9F3E-BD84B65E9158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15FDC80E-260F-9D45-AF15-8CFC33AB57D4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="6840" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dienstplan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -96,6 +96,18 @@
   </si>
   <si>
     <t>N18</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -150,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -178,19 +190,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -200,16 +199,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -558,148 +554,144 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6">
+      <c r="B1" s="5">
         <v>0</v>
       </c>
-      <c r="C1" s="6">
+      <c r="C1" s="5">
         <v>1</v>
       </c>
-      <c r="D1" s="6">
+      <c r="D1" s="5">
         <v>2</v>
       </c>
-      <c r="E1" s="6">
+      <c r="E1" s="5">
         <v>3</v>
       </c>
-      <c r="F1" s="6">
+      <c r="F1" s="5">
         <v>4</v>
       </c>
-      <c r="G1" s="6">
+      <c r="G1" s="5">
         <v>5</v>
       </c>
-      <c r="H1" s="6">
+      <c r="H1" s="5">
         <v>6</v>
       </c>
-      <c r="I1" s="6">
+      <c r="I1" s="5">
         <v>7</v>
       </c>
-      <c r="J1" s="6">
+      <c r="J1" s="5">
         <v>8</v>
       </c>
-      <c r="K1" s="6">
+      <c r="K1" s="5">
         <v>9</v>
       </c>
-      <c r="L1" s="6">
+      <c r="L1" s="5">
         <v>10</v>
       </c>
-      <c r="M1" s="6">
+      <c r="M1" s="5">
         <v>11</v>
       </c>
-      <c r="N1" s="6">
+      <c r="N1" s="5">
         <v>12</v>
       </c>
-      <c r="O1" s="6">
+      <c r="O1" s="5">
         <v>13</v>
       </c>
-      <c r="P1" s="6">
+      <c r="P1" s="5">
         <v>14</v>
       </c>
-      <c r="Q1" s="6">
+      <c r="Q1" s="5">
         <v>15</v>
       </c>
-      <c r="R1" s="6">
+      <c r="R1" s="5">
         <v>16</v>
       </c>
-      <c r="S1" s="6">
+      <c r="S1" s="5">
         <v>17</v>
       </c>
-      <c r="T1" s="6">
+      <c r="T1" s="5">
         <v>18</v>
       </c>
-      <c r="U1" s="6">
+      <c r="U1" s="5">
         <v>19</v>
       </c>
-      <c r="V1" s="6">
+      <c r="V1" s="5">
         <v>20</v>
       </c>
-      <c r="W1" s="6">
+      <c r="W1" s="5">
         <v>21</v>
       </c>
-      <c r="X1" s="6">
+      <c r="X1" s="5">
         <v>22</v>
       </c>
-      <c r="Y1" s="6">
+      <c r="Y1" s="5">
         <v>23</v>
       </c>
-      <c r="Z1" s="6">
+      <c r="Z1" s="5">
         <v>24</v>
       </c>
-      <c r="AA1" s="6">
+      <c r="AA1" s="5">
         <v>25</v>
       </c>
-      <c r="AB1" s="6">
+      <c r="AB1" s="5">
         <v>26</v>
       </c>
-      <c r="AC1" s="6">
+      <c r="AC1" s="5">
         <v>27</v>
       </c>
-      <c r="AD1" s="6">
+      <c r="AD1" s="5">
         <v>28</v>
       </c>
-      <c r="AE1" s="6">
+      <c r="AE1" s="5">
         <v>29</v>
       </c>
-      <c r="AF1" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
@@ -732,10 +724,9 @@
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
@@ -768,10 +759,9 @@
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
@@ -804,19 +794,24 @@
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -840,10 +835,9 @@
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2"/>
@@ -876,10 +870,9 @@
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2"/>
@@ -894,8 +887,12 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -912,10 +909,9 @@
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
@@ -948,10 +944,9 @@
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2"/>
@@ -959,8 +954,12 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -984,10 +983,9 @@
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2"/>
@@ -1010,7 +1008,9 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
+      <c r="V11" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
@@ -1020,10 +1020,9 @@
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
@@ -1056,10 +1055,9 @@
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2"/>
@@ -1093,10 +1091,9 @@
       <c r="AD13" s="2"/>
       <c r="AE13" s="2"/>
       <c r="AF13" s="3"/>
-      <c r="AG13" s="4"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2"/>
@@ -1119,7 +1116,9 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
+      <c r="V14" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
@@ -1129,10 +1128,9 @@
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
       <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2"/>
@@ -1165,10 +1163,9 @@
       <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
       <c r="AE15" s="2"/>
-      <c r="AF15" s="2"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
@@ -1185,8 +1182,12 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
+      <c r="P16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
@@ -1201,10 +1202,9 @@
       <c r="AC16" s="2"/>
       <c r="AD16" s="2"/>
       <c r="AE16" s="2"/>
-      <c r="AF16" s="2"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2"/>
@@ -1237,10 +1237,9 @@
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2"/>
@@ -1273,10 +1272,9 @@
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
-      <c r="AF18" s="2"/>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2"/>
@@ -1305,14 +1303,17 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
+      <c r="AB19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="AD19" s="2"/>
       <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2"/>
@@ -1345,10 +1346,9 @@
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2"/>
@@ -1365,13 +1365,27 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
+      <c r="P21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
@@ -1381,11 +1395,10 @@
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
       <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B2:AF21">
+  <conditionalFormatting sqref="B2:AE21">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",B2)))</formula>
     </cfRule>
@@ -1399,7 +1412,7 @@
       <formula>NOT(ISERROR(SEARCH("E",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG13">
+  <conditionalFormatting sqref="AF13">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>

--- a/wishes.xlsx
+++ b/wishes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="13_ncr:1_{572483D8-A287-5545-9F3E-BD84B65E9158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15FDC80E-260F-9D45-AF15-8CFC33AB57D4}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="13_ncr:1_{572483D8-A287-5545-9F3E-BD84B65E9158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A903058-65E5-9C43-99A7-B29F52F56236}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="6840" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dienstplan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -189,8 +192,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -199,13 +206,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -215,6 +219,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -558,140 +567,148 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="32" max="32" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5">
+      <c r="B1" s="4">
         <v>0</v>
       </c>
-      <c r="C1" s="5">
+      <c r="C1" s="4">
         <v>1</v>
       </c>
-      <c r="D1" s="5">
+      <c r="D1" s="4">
         <v>2</v>
       </c>
-      <c r="E1" s="5">
+      <c r="E1" s="4">
         <v>3</v>
       </c>
-      <c r="F1" s="5">
+      <c r="F1" s="4">
         <v>4</v>
       </c>
-      <c r="G1" s="5">
+      <c r="G1" s="4">
         <v>5</v>
       </c>
-      <c r="H1" s="5">
+      <c r="H1" s="4">
         <v>6</v>
       </c>
-      <c r="I1" s="5">
+      <c r="I1" s="4">
         <v>7</v>
       </c>
-      <c r="J1" s="5">
+      <c r="J1" s="4">
         <v>8</v>
       </c>
-      <c r="K1" s="5">
+      <c r="K1" s="4">
         <v>9</v>
       </c>
-      <c r="L1" s="5">
+      <c r="L1" s="4">
         <v>10</v>
       </c>
-      <c r="M1" s="5">
+      <c r="M1" s="4">
         <v>11</v>
       </c>
-      <c r="N1" s="5">
+      <c r="N1" s="4">
         <v>12</v>
       </c>
-      <c r="O1" s="5">
+      <c r="O1" s="4">
         <v>13</v>
       </c>
-      <c r="P1" s="5">
+      <c r="P1" s="4">
         <v>14</v>
       </c>
-      <c r="Q1" s="5">
+      <c r="Q1" s="4">
         <v>15</v>
       </c>
-      <c r="R1" s="5">
+      <c r="R1" s="4">
         <v>16</v>
       </c>
-      <c r="S1" s="5">
+      <c r="S1" s="4">
         <v>17</v>
       </c>
-      <c r="T1" s="5">
+      <c r="T1" s="4">
         <v>18</v>
       </c>
-      <c r="U1" s="5">
+      <c r="U1" s="4">
         <v>19</v>
       </c>
-      <c r="V1" s="5">
+      <c r="V1" s="4">
         <v>20</v>
       </c>
-      <c r="W1" s="5">
+      <c r="W1" s="4">
         <v>21</v>
       </c>
-      <c r="X1" s="5">
+      <c r="X1" s="4">
         <v>22</v>
       </c>
-      <c r="Y1" s="5">
+      <c r="Y1" s="4">
         <v>23</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="Z1" s="4">
         <v>24</v>
       </c>
-      <c r="AA1" s="5">
+      <c r="AA1" s="4">
         <v>25</v>
       </c>
-      <c r="AB1" s="5">
+      <c r="AB1" s="4">
         <v>26</v>
       </c>
-      <c r="AC1" s="5">
+      <c r="AC1" s="4">
         <v>27</v>
       </c>
-      <c r="AD1" s="5">
+      <c r="AD1" s="4">
         <v>28</v>
       </c>
-      <c r="AE1" s="5">
+      <c r="AE1" s="7">
         <v>29</v>
       </c>
+      <c r="AF1" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="8">
+        <f>COUNTIF(B2:AE2,"X")+COUNTIF(B2:AE2,"E")+COUNTIF(B2:AE2,"L")+COUNTIF(B2:AE2,"N")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
@@ -724,9 +741,13 @@
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
+      <c r="AF3" s="8">
+        <f t="shared" ref="AF3:AF21" si="0">COUNTIF(B3:AE3,"X")+COUNTIF(B3:AE3,"E")+COUNTIF(B3:AE3,"L")+COUNTIF(B3:AE3,"N")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
@@ -759,9 +780,13 @@
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
+      <c r="AF4" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
@@ -794,9 +819,13 @@
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
+      <c r="AF5" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2"/>
@@ -835,9 +864,13 @@
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
+      <c r="AF6" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2"/>
@@ -870,9 +903,13 @@
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
+      <c r="AF7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2"/>
@@ -909,9 +946,13 @@
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
+      <c r="AF8" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
@@ -944,9 +985,13 @@
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
+      <c r="AF9" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2"/>
@@ -983,9 +1028,13 @@
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
+      <c r="AF10" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2"/>
@@ -1020,9 +1069,13 @@
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
+      <c r="AF11" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
@@ -1055,9 +1108,13 @@
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
+      <c r="AF12" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2"/>
@@ -1090,10 +1147,13 @@
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
       <c r="AE13" s="2"/>
-      <c r="AF13" s="3"/>
+      <c r="AF13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2"/>
@@ -1128,9 +1188,13 @@
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
       <c r="AE14" s="2"/>
+      <c r="AF14" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2"/>
@@ -1163,9 +1227,13 @@
       <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
       <c r="AE15" s="2"/>
+      <c r="AF15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
@@ -1202,9 +1270,13 @@
       <c r="AC16" s="2"/>
       <c r="AD16" s="2"/>
       <c r="AE16" s="2"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="AF16" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2"/>
@@ -1237,9 +1309,13 @@
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="2"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="AF17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2"/>
@@ -1272,9 +1348,13 @@
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="AF18" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2"/>
@@ -1311,9 +1391,13 @@
       </c>
       <c r="AD19" s="2"/>
       <c r="AE19" s="2"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="AF19" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2"/>
@@ -1346,9 +1430,13 @@
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="AF20" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2"/>
@@ -1395,6 +1483,10 @@
       <c r="AC21" s="2"/>
       <c r="AD21" s="2"/>
       <c r="AE21" s="2"/>
+      <c r="AF21" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1412,18 +1504,6 @@
       <formula>NOT(ISERROR(SEARCH("E",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF13">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>